--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA239"/>
+  <dimension ref="A1:AA240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21213,6 +21213,93 @@
         <v>378</v>
       </c>
       <c r="AA239" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="C240" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="D240" t="n">
+        <v>363.8</v>
+      </c>
+      <c r="E240" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="F240" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="G240" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="H240" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="I240" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="J240" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="K240" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="L240" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="M240" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="N240" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="O240" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="P240" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="R240" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="S240" t="n">
+        <v>366.15</v>
+      </c>
+      <c r="T240" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="U240" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="V240" t="n">
+        <v>364.68</v>
+      </c>
+      <c r="W240" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="X240" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>369.18</v>
+      </c>
+      <c r="AA240" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21229,7 +21316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23652,6 +23739,16 @@
       </c>
       <c r="B242" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -23820,28 +23917,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02036309107515588</v>
+        <v>0.009644719537784389</v>
       </c>
       <c r="J2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004023057101339989</v>
+        <v>9.011085458787704e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>6.45188163752018</v>
+        <v>6.471565909053071</v>
       </c>
       <c r="N2" t="n">
-        <v>61.97274554477676</v>
+        <v>62.42874545426407</v>
       </c>
       <c r="O2" t="n">
-        <v>7.872277024138363</v>
+        <v>7.901186332081029</v>
       </c>
       <c r="P2" t="n">
-        <v>382.3502668657145</v>
+        <v>382.4573356335624</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23898,28 +23995,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03247559880460614</v>
+        <v>0.02432050156331647</v>
       </c>
       <c r="J3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009300433143279996</v>
+        <v>0.00052368107966827</v>
       </c>
       <c r="M3" t="n">
-        <v>6.917335840587143</v>
+        <v>6.9266753222583</v>
       </c>
       <c r="N3" t="n">
-        <v>68.14772152441955</v>
+        <v>68.27666909995763</v>
       </c>
       <c r="O3" t="n">
-        <v>8.255163325120803</v>
+        <v>8.262969750637941</v>
       </c>
       <c r="P3" t="n">
-        <v>375.8338701257764</v>
+        <v>375.9153336401041</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23976,28 +24073,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1118885652302681</v>
+        <v>-0.1173674160002454</v>
       </c>
       <c r="J4" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007559692308496513</v>
+        <v>0.008376159452031628</v>
       </c>
       <c r="M4" t="n">
-        <v>8.490445540474884</v>
+        <v>8.477846070106249</v>
       </c>
       <c r="N4" t="n">
-        <v>98.85894367287429</v>
+        <v>98.63220806002383</v>
       </c>
       <c r="O4" t="n">
-        <v>9.942783497234277</v>
+        <v>9.931374933010224</v>
       </c>
       <c r="P4" t="n">
-        <v>373.5394011132638</v>
+        <v>373.5941308638718</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24054,28 +24151,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2315335277720221</v>
+        <v>-0.2374249402083625</v>
       </c>
       <c r="J5" t="n">
+        <v>239</v>
+      </c>
+      <c r="K5" t="n">
         <v>238</v>
       </c>
-      <c r="K5" t="n">
-        <v>237</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02174174594207201</v>
+        <v>0.02302107551047838</v>
       </c>
       <c r="M5" t="n">
-        <v>10.18601841213669</v>
+        <v>10.1685561553072</v>
       </c>
       <c r="N5" t="n">
-        <v>143.3760816010754</v>
+        <v>142.9861045283864</v>
       </c>
       <c r="O5" t="n">
-        <v>11.97397517957489</v>
+        <v>11.95767973013102</v>
       </c>
       <c r="P5" t="n">
-        <v>370.5458315257338</v>
+        <v>370.6052507078473</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24132,28 +24229,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2564626388247961</v>
+        <v>-0.2716198321030214</v>
       </c>
       <c r="J6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01628162780557019</v>
+        <v>0.01829427214444923</v>
       </c>
       <c r="M6" t="n">
-        <v>12.92834676849099</v>
+        <v>12.93806489125347</v>
       </c>
       <c r="N6" t="n">
-        <v>235.9178398140581</v>
+        <v>236.3225048552563</v>
       </c>
       <c r="O6" t="n">
-        <v>15.35961717667657</v>
+        <v>15.37278455112334</v>
       </c>
       <c r="P6" t="n">
-        <v>372.9644500088826</v>
+        <v>373.1179071144969</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24210,28 +24307,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3442493237279421</v>
+        <v>-0.3555670441703753</v>
       </c>
       <c r="J7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K7" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03110547059815538</v>
+        <v>0.0333120911205842</v>
       </c>
       <c r="M7" t="n">
-        <v>12.58590211145936</v>
+        <v>12.58144293341877</v>
       </c>
       <c r="N7" t="n">
-        <v>220.2971289996927</v>
+        <v>220.1555933071792</v>
       </c>
       <c r="O7" t="n">
-        <v>14.84240981106817</v>
+        <v>14.83764109645395</v>
       </c>
       <c r="P7" t="n">
-        <v>367.0444705342853</v>
+        <v>367.1584388332388</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24288,28 +24385,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1700808473765299</v>
+        <v>-0.1881619075487216</v>
       </c>
       <c r="J8" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K8" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005622543879796216</v>
+        <v>0.00689417081066146</v>
       </c>
       <c r="M8" t="n">
-        <v>14.99290102132915</v>
+        <v>15.01812341353608</v>
       </c>
       <c r="N8" t="n">
-        <v>305.3178224324095</v>
+        <v>306.0407348770238</v>
       </c>
       <c r="O8" t="n">
-        <v>17.47334605713541</v>
+        <v>17.49401997475205</v>
       </c>
       <c r="P8" t="n">
-        <v>362.3670283937428</v>
+        <v>362.5491028389973</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24366,28 +24463,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3843808155765345</v>
+        <v>-0.3945309341227425</v>
       </c>
       <c r="J9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K9" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03749452971596556</v>
+        <v>0.03968386144956093</v>
       </c>
       <c r="M9" t="n">
-        <v>12.89788150438834</v>
+        <v>12.89101769101937</v>
       </c>
       <c r="N9" t="n">
-        <v>226.3505852594739</v>
+        <v>226.0293073945243</v>
       </c>
       <c r="O9" t="n">
-        <v>15.04495215211647</v>
+        <v>15.03427109621628</v>
       </c>
       <c r="P9" t="n">
-        <v>369.4741754001062</v>
+        <v>369.5763860661827</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24444,28 +24541,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09009260742130484</v>
+        <v>-0.09751269551936548</v>
       </c>
       <c r="J10" t="n">
+        <v>239</v>
+      </c>
+      <c r="K10" t="n">
         <v>238</v>
       </c>
-      <c r="K10" t="n">
-        <v>237</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002513499540576558</v>
+        <v>0.002966735802238607</v>
       </c>
       <c r="M10" t="n">
-        <v>11.57113896548105</v>
+        <v>11.5554108684566</v>
       </c>
       <c r="N10" t="n">
-        <v>191.4680675473289</v>
+        <v>191.0005741959588</v>
       </c>
       <c r="O10" t="n">
-        <v>13.83719868858321</v>
+        <v>13.82029573475035</v>
       </c>
       <c r="P10" t="n">
-        <v>368.0894802829474</v>
+        <v>368.1643172716595</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24522,28 +24619,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1516200320081055</v>
+        <v>-0.1649060458917988</v>
       </c>
       <c r="J11" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K11" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006860490041912803</v>
+        <v>0.008139177580073875</v>
       </c>
       <c r="M11" t="n">
-        <v>11.74316662181405</v>
+        <v>11.75210038722816</v>
       </c>
       <c r="N11" t="n">
-        <v>198.0193207017073</v>
+        <v>198.2650230135829</v>
       </c>
       <c r="O11" t="n">
-        <v>14.07193379396404</v>
+        <v>14.08066131307699</v>
       </c>
       <c r="P11" t="n">
-        <v>368.0840962022449</v>
+        <v>368.2184870576344</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24600,28 +24697,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4361697887848753</v>
+        <v>-0.4495230855246534</v>
       </c>
       <c r="J12" t="n">
+        <v>239</v>
+      </c>
+      <c r="K12" t="n">
         <v>238</v>
       </c>
-      <c r="K12" t="n">
-        <v>237</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04818191718144427</v>
+        <v>0.05125848125788923</v>
       </c>
       <c r="M12" t="n">
-        <v>12.40566465801098</v>
+        <v>12.41469454118133</v>
       </c>
       <c r="N12" t="n">
-        <v>223.3936691738399</v>
+        <v>223.5464340742267</v>
       </c>
       <c r="O12" t="n">
-        <v>14.94635972984191</v>
+        <v>14.95146929482941</v>
       </c>
       <c r="P12" t="n">
-        <v>378.9769505622275</v>
+        <v>379.1116282782031</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24678,28 +24775,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1167631599294266</v>
+        <v>-0.1285594043736272</v>
       </c>
       <c r="J13" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K13" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004670110166944186</v>
+        <v>0.005682286044608298</v>
       </c>
       <c r="M13" t="n">
-        <v>11.20460772543619</v>
+        <v>11.20748848782001</v>
       </c>
       <c r="N13" t="n">
-        <v>174.7816683502384</v>
+        <v>174.9167638094766</v>
       </c>
       <c r="O13" t="n">
-        <v>13.2205018191534</v>
+        <v>13.22561014885425</v>
       </c>
       <c r="P13" t="n">
-        <v>385.9185137342964</v>
+        <v>386.0363496717305</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24756,28 +24853,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08758575935759169</v>
+        <v>-0.09631440350767335</v>
       </c>
       <c r="J14" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K14" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002744836725794508</v>
+        <v>0.003339940866893376</v>
       </c>
       <c r="M14" t="n">
-        <v>10.69199969390825</v>
+        <v>10.68348602108014</v>
       </c>
       <c r="N14" t="n">
-        <v>167.6490348080667</v>
+        <v>167.4219520931848</v>
       </c>
       <c r="O14" t="n">
-        <v>12.94793554231974</v>
+        <v>12.93916350051984</v>
       </c>
       <c r="P14" t="n">
-        <v>385.0836372277559</v>
+        <v>385.170830060256</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24834,28 +24931,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.01577301629475496</v>
+        <v>-0.03029540488937535</v>
       </c>
       <c r="J15" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K15" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L15" t="n">
-        <v>8.937088081406586e-05</v>
+        <v>0.0003302225842880535</v>
       </c>
       <c r="M15" t="n">
-        <v>10.79569386849626</v>
+        <v>10.80857876208372</v>
       </c>
       <c r="N15" t="n">
-        <v>167.432179790298</v>
+        <v>168.0447538799277</v>
       </c>
       <c r="O15" t="n">
-        <v>12.93955871698483</v>
+        <v>12.96320770025412</v>
       </c>
       <c r="P15" t="n">
-        <v>384.5008904905885</v>
+        <v>384.6459586334134</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24912,28 +25009,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1061566057654784</v>
+        <v>-0.1197798089461605</v>
       </c>
       <c r="J16" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K16" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004288250690542617</v>
+        <v>0.005465723612462114</v>
       </c>
       <c r="M16" t="n">
-        <v>10.35750264765997</v>
+        <v>10.37393252422535</v>
       </c>
       <c r="N16" t="n">
-        <v>157.395312515252</v>
+        <v>157.8923057793494</v>
       </c>
       <c r="O16" t="n">
-        <v>12.54572885548114</v>
+        <v>12.56552051366554</v>
       </c>
       <c r="P16" t="n">
-        <v>389.2673869758414</v>
+        <v>389.4034729077026</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24990,28 +25087,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2955907835252982</v>
+        <v>-0.3113955679794044</v>
       </c>
       <c r="J17" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K17" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03287826222751256</v>
+        <v>0.03634343069977775</v>
       </c>
       <c r="M17" t="n">
-        <v>10.1093550990111</v>
+        <v>10.13811278158401</v>
       </c>
       <c r="N17" t="n">
-        <v>154.5960338798377</v>
+        <v>155.5044658237248</v>
       </c>
       <c r="O17" t="n">
-        <v>12.4336653437286</v>
+        <v>12.47014297527197</v>
       </c>
       <c r="P17" t="n">
-        <v>394.0262873773625</v>
+        <v>394.1841657259253</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25068,28 +25165,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2039977241584622</v>
+        <v>-0.2225986997058903</v>
       </c>
       <c r="J18" t="n">
+        <v>239</v>
+      </c>
+      <c r="K18" t="n">
         <v>238</v>
       </c>
-      <c r="K18" t="n">
-        <v>237</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01386340733684355</v>
+        <v>0.01642450003196261</v>
       </c>
       <c r="M18" t="n">
-        <v>10.89528599236451</v>
+        <v>10.93249276912677</v>
       </c>
       <c r="N18" t="n">
-        <v>177.3847938028188</v>
+        <v>178.7848158251944</v>
       </c>
       <c r="O18" t="n">
-        <v>13.31858828115123</v>
+        <v>13.37104393176518</v>
       </c>
       <c r="P18" t="n">
-        <v>389.7384678995513</v>
+        <v>389.9251124257544</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25146,28 +25243,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2946319411647096</v>
+        <v>-0.3088734419642714</v>
       </c>
       <c r="J19" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K19" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03081318504662822</v>
+        <v>0.03382548567902155</v>
       </c>
       <c r="M19" t="n">
-        <v>10.47708272281574</v>
+        <v>10.49711987469568</v>
       </c>
       <c r="N19" t="n">
-        <v>164.2384508597025</v>
+        <v>164.8140828322188</v>
       </c>
       <c r="O19" t="n">
-        <v>12.81555503517903</v>
+        <v>12.8379937230168</v>
       </c>
       <c r="P19" t="n">
-        <v>391.5662303744732</v>
+        <v>391.7084926516855</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -25224,28 +25321,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.266762524488658</v>
+        <v>-0.2820819246609234</v>
       </c>
       <c r="J20" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K20" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02312172875095297</v>
+        <v>0.02582303958881427</v>
       </c>
       <c r="M20" t="n">
-        <v>11.06219441482314</v>
+        <v>11.08910364598631</v>
       </c>
       <c r="N20" t="n">
-        <v>180.8481479909472</v>
+        <v>181.5526764198307</v>
       </c>
       <c r="O20" t="n">
-        <v>13.44797932742861</v>
+        <v>13.47414844878261</v>
       </c>
       <c r="P20" t="n">
-        <v>391.7726796654969</v>
+        <v>391.9257093766703</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -25302,28 +25399,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2905254392972046</v>
+        <v>-0.3035241790238523</v>
       </c>
       <c r="J21" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K21" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02694326236415401</v>
+        <v>0.02944776789451398</v>
       </c>
       <c r="M21" t="n">
-        <v>10.98452123258109</v>
+        <v>10.99867470903463</v>
       </c>
       <c r="N21" t="n">
-        <v>183.3583101147021</v>
+        <v>183.6431627486129</v>
       </c>
       <c r="O21" t="n">
-        <v>13.54098630509248</v>
+        <v>13.5515003873598</v>
       </c>
       <c r="P21" t="n">
-        <v>396.1732274169174</v>
+        <v>396.3030754112004</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -25380,28 +25477,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.08504748935581664</v>
+        <v>-0.1005812397184294</v>
       </c>
       <c r="J22" t="n">
+        <v>239</v>
+      </c>
+      <c r="K22" t="n">
         <v>238</v>
       </c>
-      <c r="K22" t="n">
-        <v>237</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.001471517286863566</v>
+        <v>0.002066309821799006</v>
       </c>
       <c r="M22" t="n">
-        <v>13.74619585592259</v>
+        <v>13.76801186153439</v>
       </c>
       <c r="N22" t="n">
-        <v>296.4123759078499</v>
+        <v>296.676904205235</v>
       </c>
       <c r="O22" t="n">
-        <v>17.21663079431774</v>
+        <v>17.22431142905965</v>
       </c>
       <c r="P22" t="n">
-        <v>386.0564503981444</v>
+        <v>386.2113705218036</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25458,28 +25555,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2215873664393778</v>
+        <v>-0.2511821727652404</v>
       </c>
       <c r="J23" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K23" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="n">
-        <v>0.008817271289507933</v>
+        <v>0.01122682197674685</v>
       </c>
       <c r="M23" t="n">
-        <v>15.08385898291249</v>
+        <v>15.18373938972374</v>
       </c>
       <c r="N23" t="n">
-        <v>331.6598893220943</v>
+        <v>335.7085074966099</v>
       </c>
       <c r="O23" t="n">
-        <v>18.21153176759424</v>
+        <v>18.32234994471533</v>
       </c>
       <c r="P23" t="n">
-        <v>384.225481109034</v>
+        <v>384.5222211674107</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25536,28 +25633,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1702007859052221</v>
+        <v>0.1495476850067042</v>
       </c>
       <c r="J24" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K24" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L24" t="n">
-        <v>0.006411241666006151</v>
+        <v>0.004956229336723461</v>
       </c>
       <c r="M24" t="n">
-        <v>13.39806057719913</v>
+        <v>13.45253451965411</v>
       </c>
       <c r="N24" t="n">
-        <v>268.4327941735403</v>
+        <v>269.9329580047861</v>
       </c>
       <c r="O24" t="n">
-        <v>16.38391876730168</v>
+        <v>16.42963657555413</v>
       </c>
       <c r="P24" t="n">
-        <v>381.717821439375</v>
+        <v>381.9259817926806</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25614,28 +25711,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2819656147920953</v>
+        <v>0.2634857946848528</v>
       </c>
       <c r="J25" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K25" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01992103380882826</v>
+        <v>0.01745054781501854</v>
       </c>
       <c r="M25" t="n">
-        <v>12.46107835673496</v>
+        <v>12.50119341365994</v>
       </c>
       <c r="N25" t="n">
-        <v>233.8780287111146</v>
+        <v>234.9987209171496</v>
       </c>
       <c r="O25" t="n">
-        <v>15.29307126482822</v>
+        <v>15.32966799761657</v>
       </c>
       <c r="P25" t="n">
-        <v>383.7280152735815</v>
+        <v>383.9142713666228</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25692,28 +25789,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1988900985109812</v>
+        <v>0.1810209717554357</v>
       </c>
       <c r="J26" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K26" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01151844213720632</v>
+        <v>0.009560151193647948</v>
       </c>
       <c r="M26" t="n">
-        <v>11.30577915030915</v>
+        <v>11.3461841651339</v>
       </c>
       <c r="N26" t="n">
-        <v>202.9780519167281</v>
+        <v>204.0924137194374</v>
       </c>
       <c r="O26" t="n">
-        <v>14.24703660122792</v>
+        <v>14.28609161805416</v>
       </c>
       <c r="P26" t="n">
-        <v>385.5635845754298</v>
+        <v>385.743685556729</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25751,7 +25848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA239"/>
+  <dimension ref="A1:AA240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58385,6 +58482,143 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-34.77189787455751,173.14919002639726</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>-34.77245097390679,173.14859650058094</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-34.77304385040144,173.14807446003616</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-34.77369182731454,173.14763794753287</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-34.77434789353511,173.14716517675288</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-34.77509105518223,173.14698063106218</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-34.77583089560954,173.1467651604477</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-34.776587703832156,173.14688513095695</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-34.77732809748477,173.1470365029881</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-34.77807329750991,173.14709214807365</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-34.77879497210005,173.14728812575154</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>-34.77948906503323,173.14763513406808</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-34.78015733933828,173.14799569610346</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>-34.78085353973048,173.14829514450304</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>-34.7815163195695,173.14868677663083</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>-34.78217935690345,173.14906818804192</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>-34.78282495648287,173.14950431037778</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>-34.783423877130964,173.15003117559039</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>-34.78404719477483,173.15051182640403</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>-34.784633593754045,173.15105464365647</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>-34.78525471712749,173.15153652580818</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>-34.78595067551452,173.15192064328028</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>-34.78641532625176,173.15264561441273</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>-34.7869539462696,173.153264549627</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>-34.787533296920024,173.15382073006336</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA240"/>
+  <dimension ref="A1:AA241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21302,6 +21302,93 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="C241" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="D241" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="E241" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="F241" t="n">
+        <v>353.86</v>
+      </c>
+      <c r="G241" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="H241" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="I241" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="J241" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="K241" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="L241" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="M241" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="N241" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="O241" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="P241" t="n">
+        <v>371.04</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="R241" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="S241" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="T241" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="U241" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="V241" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="W241" t="n">
+        <v>348.05</v>
+      </c>
+      <c r="X241" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21316,7 +21403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B243"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23749,6 +23836,16 @@
       </c>
       <c r="B243" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -23917,28 +24014,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009644719537784389</v>
+        <v>0.001159186400369259</v>
       </c>
       <c r="J2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>9.011085458787704e-05</v>
+        <v>1.304989951655955e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>6.471565909053071</v>
+        <v>6.481495273914055</v>
       </c>
       <c r="N2" t="n">
-        <v>62.42874545426407</v>
+        <v>62.6191960633201</v>
       </c>
       <c r="O2" t="n">
-        <v>7.901186332081029</v>
+        <v>7.913229180512852</v>
       </c>
       <c r="P2" t="n">
-        <v>382.4573356335624</v>
+        <v>382.5425020837416</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23995,28 +24092,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02432050156331647</v>
+        <v>0.01869477626988506</v>
       </c>
       <c r="J3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00052368107966827</v>
+        <v>0.0003115958974064803</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9266753222583</v>
+        <v>6.924322728165208</v>
       </c>
       <c r="N3" t="n">
-        <v>68.27666909995763</v>
+        <v>68.19022685381488</v>
       </c>
       <c r="O3" t="n">
-        <v>8.262969750637941</v>
+        <v>8.257737393125</v>
       </c>
       <c r="P3" t="n">
-        <v>375.9153336401041</v>
+        <v>375.9717971580902</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24073,28 +24170,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1173674160002454</v>
+        <v>-0.1201276738825822</v>
       </c>
       <c r="J4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008376159452031628</v>
+        <v>0.008851509846518613</v>
       </c>
       <c r="M4" t="n">
-        <v>8.477846070106249</v>
+        <v>8.453901375196264</v>
       </c>
       <c r="N4" t="n">
-        <v>98.63220806002383</v>
+        <v>98.26891695225085</v>
       </c>
       <c r="O4" t="n">
-        <v>9.931374933010224</v>
+        <v>9.913067988884714</v>
       </c>
       <c r="P4" t="n">
-        <v>373.5941308638718</v>
+        <v>373.6218346464876</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24151,28 +24248,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2374249402083625</v>
+        <v>-0.2401713187568142</v>
       </c>
       <c r="J5" t="n">
+        <v>240</v>
+      </c>
+      <c r="K5" t="n">
         <v>239</v>
       </c>
-      <c r="K5" t="n">
-        <v>238</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02302107551047838</v>
+        <v>0.02376113088081511</v>
       </c>
       <c r="M5" t="n">
-        <v>10.1685561553072</v>
+        <v>10.13764948324485</v>
       </c>
       <c r="N5" t="n">
-        <v>142.9861045283864</v>
+        <v>142.4342351684693</v>
       </c>
       <c r="O5" t="n">
-        <v>11.95767973013102</v>
+        <v>11.93458148275294</v>
       </c>
       <c r="P5" t="n">
-        <v>370.6052507078473</v>
+        <v>370.6330799453673</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24229,28 +24326,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2716198321030214</v>
+        <v>-0.2814307545770772</v>
       </c>
       <c r="J6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01829427214444923</v>
+        <v>0.0197525196102134</v>
       </c>
       <c r="M6" t="n">
-        <v>12.93806489125347</v>
+        <v>12.92480717788962</v>
       </c>
       <c r="N6" t="n">
-        <v>236.3225048552563</v>
+        <v>235.9166605930222</v>
       </c>
       <c r="O6" t="n">
-        <v>15.37278455112334</v>
+        <v>15.35957878957044</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1179071144969</v>
+        <v>373.2177049303448</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24307,28 +24404,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3555670441703753</v>
+        <v>-0.3629002153215857</v>
       </c>
       <c r="J7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K7" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0333120911205842</v>
+        <v>0.03492743689777467</v>
       </c>
       <c r="M7" t="n">
-        <v>12.58144293341877</v>
+        <v>12.55962951083549</v>
       </c>
       <c r="N7" t="n">
-        <v>220.1555933071792</v>
+        <v>219.5630458961216</v>
       </c>
       <c r="O7" t="n">
-        <v>14.83764109645395</v>
+        <v>14.81765993320543</v>
       </c>
       <c r="P7" t="n">
-        <v>367.1584388332388</v>
+        <v>367.2326321177226</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24385,28 +24482,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1881619075487216</v>
+        <v>-0.2011814164051368</v>
       </c>
       <c r="J8" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K8" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00689417081066146</v>
+        <v>0.007922664224125686</v>
       </c>
       <c r="M8" t="n">
-        <v>15.01812341353608</v>
+        <v>15.01807819487992</v>
       </c>
       <c r="N8" t="n">
-        <v>306.0407348770238</v>
+        <v>305.802860769295</v>
       </c>
       <c r="O8" t="n">
-        <v>17.49401997475205</v>
+        <v>17.48721992682928</v>
       </c>
       <c r="P8" t="n">
-        <v>362.5491028389973</v>
+        <v>362.6808275873369</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24463,28 +24560,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3945309341227425</v>
+        <v>-0.4004620380819325</v>
       </c>
       <c r="J9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03968386144956093</v>
+        <v>0.04118085394581561</v>
       </c>
       <c r="M9" t="n">
-        <v>12.89101769101937</v>
+        <v>12.86454204976065</v>
       </c>
       <c r="N9" t="n">
-        <v>226.0293073945243</v>
+        <v>225.2970987069147</v>
       </c>
       <c r="O9" t="n">
-        <v>15.03427109621628</v>
+        <v>15.00990002321517</v>
       </c>
       <c r="P9" t="n">
-        <v>369.5763860661827</v>
+        <v>369.6363939501218</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24541,28 +24638,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09751269551936548</v>
+        <v>-0.1023769305521499</v>
       </c>
       <c r="J10" t="n">
+        <v>240</v>
+      </c>
+      <c r="K10" t="n">
         <v>239</v>
       </c>
-      <c r="K10" t="n">
-        <v>238</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002966735802238607</v>
+        <v>0.003298424311857673</v>
       </c>
       <c r="M10" t="n">
-        <v>11.5554108684566</v>
+        <v>11.52890180064442</v>
       </c>
       <c r="N10" t="n">
-        <v>191.0005741959588</v>
+        <v>190.3469597548085</v>
       </c>
       <c r="O10" t="n">
-        <v>13.82029573475035</v>
+        <v>13.79662856479105</v>
       </c>
       <c r="P10" t="n">
-        <v>368.1643172716595</v>
+        <v>368.2136068905859</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24619,28 +24716,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1649060458917988</v>
+        <v>-0.1747247953077865</v>
       </c>
       <c r="J11" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K11" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008139177580073875</v>
+        <v>0.009188801368870014</v>
       </c>
       <c r="M11" t="n">
-        <v>11.75210038722816</v>
+        <v>11.74585195101038</v>
       </c>
       <c r="N11" t="n">
-        <v>198.2650230135829</v>
+        <v>198.0238350025932</v>
       </c>
       <c r="O11" t="n">
-        <v>14.08066131307699</v>
+        <v>14.07209419392129</v>
       </c>
       <c r="P11" t="n">
-        <v>368.2184870576344</v>
+        <v>368.3182759540636</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24697,28 +24794,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4495230855246534</v>
+        <v>-0.4589635295113195</v>
       </c>
       <c r="J12" t="n">
+        <v>240</v>
+      </c>
+      <c r="K12" t="n">
         <v>239</v>
       </c>
-      <c r="K12" t="n">
-        <v>238</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.05125848125788923</v>
+        <v>0.05368583954189632</v>
       </c>
       <c r="M12" t="n">
-        <v>12.41469454118133</v>
+        <v>12.40551989987436</v>
       </c>
       <c r="N12" t="n">
-        <v>223.5464340742267</v>
+        <v>223.1593341453315</v>
       </c>
       <c r="O12" t="n">
-        <v>14.95146929482941</v>
+        <v>14.93851847223584</v>
       </c>
       <c r="P12" t="n">
-        <v>379.1116282782031</v>
+        <v>379.207288928534</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24775,28 +24872,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1285594043736272</v>
+        <v>-0.138864214056088</v>
       </c>
       <c r="J13" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K13" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005682286044608298</v>
+        <v>0.006662153952399441</v>
       </c>
       <c r="M13" t="n">
-        <v>11.20748848782001</v>
+        <v>11.20371810362686</v>
       </c>
       <c r="N13" t="n">
-        <v>174.9167638094766</v>
+        <v>174.8524276464576</v>
       </c>
       <c r="O13" t="n">
-        <v>13.22561014885425</v>
+        <v>13.22317766826331</v>
       </c>
       <c r="P13" t="n">
-        <v>386.0363496717305</v>
+        <v>386.1397755904342</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24853,28 +24950,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09631440350767335</v>
+        <v>-0.1038709339891342</v>
       </c>
       <c r="J14" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K14" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003339940866893376</v>
+        <v>0.003911701992152516</v>
       </c>
       <c r="M14" t="n">
-        <v>10.68348602108014</v>
+        <v>10.66987119001731</v>
       </c>
       <c r="N14" t="n">
-        <v>167.4219520931848</v>
+        <v>167.0816739817372</v>
       </c>
       <c r="O14" t="n">
-        <v>12.93916350051984</v>
+        <v>12.92600765827319</v>
       </c>
       <c r="P14" t="n">
-        <v>385.170830060256</v>
+        <v>385.246672422351</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24931,28 +25028,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03029540488937535</v>
+        <v>-0.04307996535641679</v>
       </c>
       <c r="J15" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K15" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003302225842880535</v>
+        <v>0.0006699007974462212</v>
       </c>
       <c r="M15" t="n">
-        <v>10.80857876208372</v>
+        <v>10.81471944286514</v>
       </c>
       <c r="N15" t="n">
-        <v>168.0447538799277</v>
+        <v>168.3673326832035</v>
       </c>
       <c r="O15" t="n">
-        <v>12.96320770025412</v>
+        <v>12.97564382538314</v>
       </c>
       <c r="P15" t="n">
-        <v>384.6459586334134</v>
+        <v>384.7742729790706</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25009,28 +25106,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1197798089461605</v>
+        <v>-0.132041044222118</v>
       </c>
       <c r="J16" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K16" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005465723612462114</v>
+        <v>0.006658658983372923</v>
       </c>
       <c r="M16" t="n">
-        <v>10.37393252422535</v>
+        <v>10.38536373012175</v>
       </c>
       <c r="N16" t="n">
-        <v>157.8923057793494</v>
+        <v>158.1751681338157</v>
       </c>
       <c r="O16" t="n">
-        <v>12.56552051366554</v>
+        <v>12.57677097405434</v>
       </c>
       <c r="P16" t="n">
-        <v>389.4034729077026</v>
+        <v>389.5265348139323</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25087,28 +25184,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3113955679794044</v>
+        <v>-0.3254403441627213</v>
       </c>
       <c r="J17" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K17" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03634343069977775</v>
+        <v>0.03962898911886592</v>
       </c>
       <c r="M17" t="n">
-        <v>10.13811278158401</v>
+        <v>10.16013204939887</v>
       </c>
       <c r="N17" t="n">
-        <v>155.5044658237248</v>
+        <v>156.0908683179774</v>
       </c>
       <c r="O17" t="n">
-        <v>12.47014297527197</v>
+        <v>12.49363311122819</v>
       </c>
       <c r="P17" t="n">
-        <v>394.1841657259253</v>
+        <v>394.3251284340692</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25165,28 +25262,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2225986997058903</v>
+        <v>-0.2389352950283588</v>
       </c>
       <c r="J18" t="n">
+        <v>240</v>
+      </c>
+      <c r="K18" t="n">
         <v>239</v>
       </c>
-      <c r="K18" t="n">
-        <v>238</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01642450003196261</v>
+        <v>0.01888358558556547</v>
       </c>
       <c r="M18" t="n">
-        <v>10.93249276912677</v>
+        <v>10.95858691812687</v>
       </c>
       <c r="N18" t="n">
-        <v>178.7848158251944</v>
+        <v>179.6997948951235</v>
       </c>
       <c r="O18" t="n">
-        <v>13.37104393176518</v>
+        <v>13.40521521256274</v>
       </c>
       <c r="P18" t="n">
-        <v>389.9251124257544</v>
+        <v>390.0898130149255</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25243,28 +25340,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3088734419642714</v>
+        <v>-0.3215655206369402</v>
       </c>
       <c r="J19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03382548567902155</v>
+        <v>0.03668396585659262</v>
       </c>
       <c r="M19" t="n">
-        <v>10.49711987469568</v>
+        <v>10.51010890762531</v>
       </c>
       <c r="N19" t="n">
-        <v>164.8140828322188</v>
+        <v>165.1353791914827</v>
       </c>
       <c r="O19" t="n">
-        <v>12.8379937230168</v>
+        <v>12.85050112608387</v>
       </c>
       <c r="P19" t="n">
-        <v>391.7084926516855</v>
+        <v>391.8358787885896</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -25321,28 +25418,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2820819246609234</v>
+        <v>-0.2944977356449602</v>
       </c>
       <c r="J20" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K20" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02582303958881427</v>
+        <v>0.02820000585861726</v>
       </c>
       <c r="M20" t="n">
-        <v>11.08910364598631</v>
+        <v>11.10139971585573</v>
       </c>
       <c r="N20" t="n">
-        <v>181.5526764198307</v>
+        <v>181.7608231476759</v>
       </c>
       <c r="O20" t="n">
-        <v>13.47414844878261</v>
+        <v>13.48187016506523</v>
       </c>
       <c r="P20" t="n">
-        <v>391.9257093766703</v>
+        <v>392.0503227074397</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -25399,28 +25496,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3035241790238523</v>
+        <v>-0.3134696682042535</v>
       </c>
       <c r="J21" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K21" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02944776789451398</v>
+        <v>0.03153936008416203</v>
       </c>
       <c r="M21" t="n">
-        <v>10.99867470903463</v>
+        <v>10.99851737149381</v>
       </c>
       <c r="N21" t="n">
-        <v>183.6431627486129</v>
+        <v>183.4969344767669</v>
       </c>
       <c r="O21" t="n">
-        <v>13.5515003873598</v>
+        <v>13.54610403314425</v>
       </c>
       <c r="P21" t="n">
-        <v>396.3030754112004</v>
+        <v>396.4028949505357</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -25477,28 +25574,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1005812397184294</v>
+        <v>-0.1125670774285645</v>
       </c>
       <c r="J22" t="n">
+        <v>240</v>
+      </c>
+      <c r="K22" t="n">
         <v>239</v>
       </c>
-      <c r="K22" t="n">
-        <v>238</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.002066309821799006</v>
+        <v>0.002603874414200846</v>
       </c>
       <c r="M22" t="n">
-        <v>13.76801186153439</v>
+        <v>13.77254459584592</v>
       </c>
       <c r="N22" t="n">
-        <v>296.676904205235</v>
+        <v>296.3390538375605</v>
       </c>
       <c r="O22" t="n">
-        <v>17.22431142905965</v>
+        <v>17.21450126601292</v>
       </c>
       <c r="P22" t="n">
-        <v>386.2113705218036</v>
+        <v>386.3314778366309</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25555,28 +25652,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2511821727652404</v>
+        <v>-0.2753540533591634</v>
       </c>
       <c r="J23" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K23" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01122682197674685</v>
+        <v>0.01344520494779189</v>
       </c>
       <c r="M23" t="n">
-        <v>15.18373938972374</v>
+        <v>15.25178684219262</v>
       </c>
       <c r="N23" t="n">
-        <v>335.7085074966099</v>
+        <v>337.9503688314184</v>
       </c>
       <c r="O23" t="n">
-        <v>18.32234994471533</v>
+        <v>18.38342647145571</v>
       </c>
       <c r="P23" t="n">
-        <v>384.5222211674107</v>
+        <v>384.7657421233423</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25633,28 +25730,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1495476850067042</v>
+        <v>0.1309735394938696</v>
       </c>
       <c r="J24" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K24" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004956229336723461</v>
+        <v>0.003812520488253646</v>
       </c>
       <c r="M24" t="n">
-        <v>13.45253451965411</v>
+        <v>13.49454814674779</v>
       </c>
       <c r="N24" t="n">
-        <v>269.9329580047861</v>
+        <v>270.9378148334488</v>
       </c>
       <c r="O24" t="n">
-        <v>16.42963657555413</v>
+        <v>16.46018878486662</v>
       </c>
       <c r="P24" t="n">
-        <v>381.9259817926806</v>
+        <v>382.1140791859792</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25711,28 +25808,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2634857946848528</v>
+        <v>0.2473963384778875</v>
       </c>
       <c r="J25" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K25" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01745054781501854</v>
+        <v>0.01545928642104311</v>
       </c>
       <c r="M25" t="n">
-        <v>12.50119341365994</v>
+        <v>12.52946585881195</v>
       </c>
       <c r="N25" t="n">
-        <v>234.9987209171496</v>
+        <v>235.6157806001528</v>
       </c>
       <c r="O25" t="n">
-        <v>15.32966799761657</v>
+        <v>15.34978112548035</v>
       </c>
       <c r="P25" t="n">
-        <v>383.9142713666228</v>
+        <v>384.0772067097334</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25789,28 +25886,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1810209717554357</v>
+        <v>0.1657369922783257</v>
       </c>
       <c r="J26" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K26" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L26" t="n">
-        <v>0.009560151193647948</v>
+        <v>0.00804678218967092</v>
       </c>
       <c r="M26" t="n">
-        <v>11.3461841651339</v>
+        <v>11.37285198793109</v>
       </c>
       <c r="N26" t="n">
-        <v>204.0924137194374</v>
+        <v>204.6828490545438</v>
       </c>
       <c r="O26" t="n">
-        <v>14.28609161805416</v>
+        <v>14.30674138490466</v>
       </c>
       <c r="P26" t="n">
-        <v>385.743685556729</v>
+        <v>385.8984639661524</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25848,7 +25945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA240"/>
+  <dimension ref="A1:AA241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58619,6 +58716,143 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-34.77191222048161,173.1492113846894</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-34.772466717112955,173.1486223524229</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-34.77305789818265,173.14810525790259</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-34.773705439043695,173.147674626238</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-34.77436361511698,173.14722940353863</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-34.775097045880955,173.14703015590385</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-34.77583441380412,173.1468278571461</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-34.77658658612666,173.1469385568851</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-34.77732523496631,173.1470684468712</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-34.77806716568239,173.1471342302971</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-34.77878775478939,173.1473356349284</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-34.77948522603974,173.14765153684903</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-34.78015308167589,173.14800822785324</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-34.78084703241179,173.14831328693404</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>-34.781511050592506,173.1487001992976</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>-34.782171328239826,173.14908503458742</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>-34.78281358200531,173.14952585253377</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>-34.78341634271404,173.1500454450382</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>-34.78403159116448,173.15054137813016</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>-34.78461569052438,173.15108534940464</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>-34.785231976803644,173.1515707449549</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>-34.78591653082171,173.15197109356689</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>-34.78640354654765,173.15266358687887</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>-34.78693983819395,173.15328642140045</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>-34.78751791127171,173.1538445824502</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
